--- a/Assets/Resources/Data/Excel/TextData.xlsx
+++ b/Assets/Resources/Data/Excel/TextData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\grunge\Assets\Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BFB6F9-5954-423F-AF64-994E96889B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A7F657-E4D8-4A2E-BF67-601216CA4204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{D3CC564E-66F4-4F1F-9FD0-0A2B28A7B6F6}"/>
+    <workbookView minimized="1" xWindow="4275" yWindow="3390" windowWidth="21600" windowHeight="10740" xr2:uid="{D3CC564E-66F4-4F1F-9FD0-0A2B28A7B6F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -231,43 +231,438 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Hammer Jack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLEED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLOCK SIGHT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MARK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STUN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOWN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOVE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEATH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cup noodle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meal-kit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rotten bread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rotten meal-kit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>latte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rotten latte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energy drink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>water</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coffee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>espresso</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rotten coffee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stimulant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lollipop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cigarette</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>whisky</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>band-aid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bandage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>first-aid-kit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detoxicant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sedative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lockpick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Old man's diary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F.Galton's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'R.Weikart's Note</t>
+  </si>
+  <si>
+    <t>N.Tesla's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.Hubbard's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O.Holmes' Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>J.Cousteau's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M.Grant's Note-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L.Darwin's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>W.Churchill's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M.Grant's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C.Darwin's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M.Sanger's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F.Osborn's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T.Dobzhansky's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T.Turner's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B.Russell's Note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Survivor's chipset-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Survivor's chipset-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Survivor's chipset-3</t>
+  </si>
+  <si>
+    <t>Survivor's chipset-4</t>
+  </si>
+  <si>
+    <t>Survivor's chipset-5</t>
+  </si>
+  <si>
+    <t>Survivor's chipset-6</t>
+  </si>
+  <si>
+    <t>Survivor's chipset-7</t>
+  </si>
+  <si>
+    <t>Damaged chipset-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damaged chipset-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damaged chipset-3</t>
+  </si>
+  <si>
+    <t>Damaged chipset-4</t>
+  </si>
+  <si>
+    <t>Damaged chipset-5</t>
+  </si>
+  <si>
+    <t>Damaged chipset-6</t>
+  </si>
+  <si>
+    <t>Damaged chipset-7</t>
+  </si>
+  <si>
+    <t>Damaged chipset-8</t>
+  </si>
+  <si>
+    <t>Damaged chipset-9</t>
+  </si>
+  <si>
+    <t>Bracelet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diamond Ring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XTECH Brochure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XTECH Brochure-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VR Gear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xperience Brochure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMA Gloves</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Handcuffs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nine Pilgrims Brochure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cross</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nine Pilgrims Ring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nine Pilgrims Bible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Upgrade Kit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy is here!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Had to clear scrapped metal.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Had to remove scattered stuffs.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seems there was an enemy. Being vigilant, but nothing happened.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Couldn’t see ahead, so walked slowly with cautious.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown noise, but faded. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unknown noise was keep going.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stomach is rubling.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Sudden hunger came. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thought we found something edible, but wasn't.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Stink odor covered nose. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deeply stabbed by something sharp.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stumbled over rubble.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>There was a trap underfoot.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Who am I, and where am I….</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sat for a while thinking that nothing would happen.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lay for a while thinking that nothing would happen.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Found a walkman and listened to music. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Found a tobacco, and burned one.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Found fruits, and ate it.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Found snacks, and ate it.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Found first aid, and took it. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>For some reason, felt strength.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Screen Man</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hollow Brigand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Rabbit Woman</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Spectre Skiver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Barber D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Despairer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Hammer Jack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BLEED</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BLOCK SIGHT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MARK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STUN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DOWN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MOVE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEATH</t>
+    <t>Silence Head</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sirena</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ghoul Dog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Smiley Hag</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -635,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C61FB5-AAE8-41CA-A521-D7E0986A0FE0}">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B162"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="23.58203125" customWidth="1"/>
@@ -694,7 +1089,7 @@
         <v>2000</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -702,7 +1097,7 @@
         <v>2001</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -710,415 +1105,1231 @@
         <v>2002</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>10000</v>
+        <v>2003</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>10001</v>
+        <v>2004</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>10002</v>
+        <v>2005</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>10003</v>
+        <v>2006</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>10010</v>
+        <v>2007</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>10011</v>
+        <v>2008</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>10012</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+        <v>2009</v>
+      </c>
+      <c r="B16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>10013</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>2010</v>
+      </c>
+      <c r="B17" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>10014</v>
+        <v>10000</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>10015</v>
+        <v>10001</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>10020</v>
+        <v>10002</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>10021</v>
+        <v>10003</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22">
-        <v>10022</v>
+        <v>10010</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23">
-        <v>10098</v>
+        <v>10011</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>10099</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+        <v>10012</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="34" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>11000</v>
-      </c>
-      <c r="B25" t="s">
-        <v>13</v>
+        <v>10013</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26">
-        <v>11001</v>
+        <v>10014</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>11002</v>
+        <v>10015</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28">
-        <v>11003</v>
+        <v>10020</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29">
-        <v>11004</v>
+        <v>10021</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>11005</v>
+        <v>10022</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31">
-        <v>11006</v>
+        <v>10098</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32">
-        <v>11010</v>
+        <v>10099</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33">
-        <v>11011</v>
+        <v>11000</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34">
-        <v>11012</v>
+        <v>11001</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35">
-        <v>11020</v>
+        <v>11002</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36">
-        <v>11021</v>
+        <v>11003</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37">
-        <v>11022</v>
+        <v>11004</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38">
-        <v>11023</v>
+        <v>11005</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39">
-        <v>11024</v>
+        <v>11006</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40">
-        <v>11025</v>
+        <v>11010</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41">
-        <v>11030</v>
+        <v>11011</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42">
-        <v>11031</v>
+        <v>11012</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43">
-        <v>11040</v>
+        <v>11020</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44">
-        <v>11041</v>
+        <v>11021</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45">
-        <v>11042</v>
+        <v>11022</v>
       </c>
       <c r="B45" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46">
-        <v>12000</v>
+        <v>11023</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47">
-        <v>12001</v>
+        <v>11024</v>
       </c>
       <c r="B47" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48">
-        <v>12002</v>
+        <v>11025</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49">
-        <v>12003</v>
+        <v>11030</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50">
-        <v>12004</v>
+        <v>11031</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51">
-        <v>12005</v>
+        <v>11040</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52">
-        <v>12006</v>
+        <v>11041</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53">
-        <v>12007</v>
+        <v>11042</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A54">
-        <v>12010</v>
+        <v>12000</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A55">
-        <v>12011</v>
+        <v>12001</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A56">
-        <v>12012</v>
+        <v>12002</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A57">
-        <v>12013</v>
+        <v>12003</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A58">
-        <v>12014</v>
+        <v>12004</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A59">
-        <v>12015</v>
+        <v>12005</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A60">
+        <v>12006</v>
+      </c>
+      <c r="B60" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>12007</v>
+      </c>
+      <c r="B61" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>12010</v>
+      </c>
+      <c r="B62" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>12011</v>
+      </c>
+      <c r="B63" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <v>12012</v>
+      </c>
+      <c r="B64" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>12013</v>
+      </c>
+      <c r="B65" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A66">
+        <v>12014</v>
+      </c>
+      <c r="B66" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>12015</v>
+      </c>
+      <c r="B67" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A68">
         <v>12016</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B68" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <v>20000</v>
+      </c>
+      <c r="B69" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <v>20001</v>
+      </c>
+      <c r="B70" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <v>20002</v>
+      </c>
+      <c r="B71" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>20003</v>
+      </c>
+      <c r="B72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A73">
+        <v>20004</v>
+      </c>
+      <c r="B73" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <v>20005</v>
+      </c>
+      <c r="B74" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A75">
+        <v>20006</v>
+      </c>
+      <c r="B75" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A76">
+        <v>20007</v>
+      </c>
+      <c r="B76" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A77">
+        <v>20008</v>
+      </c>
+      <c r="B77" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A78">
+        <v>20009</v>
+      </c>
+      <c r="B78" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A79">
+        <v>20010</v>
+      </c>
+      <c r="B79" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A80">
+        <v>20011</v>
+      </c>
+      <c r="B80" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A81">
+        <v>20012</v>
+      </c>
+      <c r="B81" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A82">
+        <v>20013</v>
+      </c>
+      <c r="B82" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A83">
+        <v>20014</v>
+      </c>
+      <c r="B83" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A84">
+        <v>20015</v>
+      </c>
+      <c r="B84" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A85">
+        <v>20016</v>
+      </c>
+      <c r="B85" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A86">
+        <v>20017</v>
+      </c>
+      <c r="B86" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A87">
+        <v>20018</v>
+      </c>
+      <c r="B87" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A88">
+        <v>21000</v>
+      </c>
+      <c r="B88" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A89">
+        <v>21001</v>
+      </c>
+      <c r="B89" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A90">
+        <v>21002</v>
+      </c>
+      <c r="B90" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A91">
+        <v>21003</v>
+      </c>
+      <c r="B91" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A92">
+        <v>21004</v>
+      </c>
+      <c r="B92" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A93">
+        <v>21005</v>
+      </c>
+      <c r="B93" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A94">
+        <v>22000</v>
+      </c>
+      <c r="B94" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A95">
+        <v>22001</v>
+      </c>
+      <c r="B95" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A96">
+        <v>22002</v>
+      </c>
+      <c r="B96" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A97">
+        <v>22003</v>
+      </c>
+      <c r="B97" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A98">
+        <v>22004</v>
+      </c>
+      <c r="B98" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A99">
+        <v>22005</v>
+      </c>
+      <c r="B99" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A100">
+        <v>22006</v>
+      </c>
+      <c r="B100" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A101">
+        <v>22007</v>
+      </c>
+      <c r="B101" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A102">
+        <v>22008</v>
+      </c>
+      <c r="B102" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A103">
+        <v>22009</v>
+      </c>
+      <c r="B103" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A104">
+        <v>22010</v>
+      </c>
+      <c r="B104" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A105">
+        <v>22011</v>
+      </c>
+      <c r="B105" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A106">
+        <v>22012</v>
+      </c>
+      <c r="B106" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A107">
+        <v>22013</v>
+      </c>
+      <c r="B107" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A108">
+        <v>22014</v>
+      </c>
+      <c r="B108" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A109">
+        <v>22015</v>
+      </c>
+      <c r="B109" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A110">
+        <v>22016</v>
+      </c>
+      <c r="B110" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A111">
+        <v>22020</v>
+      </c>
+      <c r="B111" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A112">
+        <v>22021</v>
+      </c>
+      <c r="B112" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A113">
+        <v>22022</v>
+      </c>
+      <c r="B113" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A114">
+        <v>22023</v>
+      </c>
+      <c r="B114" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A115">
+        <v>22024</v>
+      </c>
+      <c r="B115" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A116">
+        <v>22025</v>
+      </c>
+      <c r="B116" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A117">
+        <v>22026</v>
+      </c>
+      <c r="B117" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A118">
+        <v>22027</v>
+      </c>
+      <c r="B118" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A119">
+        <v>22028</v>
+      </c>
+      <c r="B119" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A120">
+        <v>22029</v>
+      </c>
+      <c r="B120" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A121">
+        <v>22030</v>
+      </c>
+      <c r="B121" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A122">
+        <v>22031</v>
+      </c>
+      <c r="B122" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A123">
+        <v>22032</v>
+      </c>
+      <c r="B123" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A124">
+        <v>22033</v>
+      </c>
+      <c r="B124" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A125">
+        <v>22034</v>
+      </c>
+      <c r="B125" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A126">
+        <v>22035</v>
+      </c>
+      <c r="B126" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A127">
+        <v>23000</v>
+      </c>
+      <c r="B127" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A128">
+        <v>23001</v>
+      </c>
+      <c r="B128" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A129">
+        <v>23002</v>
+      </c>
+      <c r="B129" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A130">
+        <v>23003</v>
+      </c>
+      <c r="B130" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A131">
+        <v>23004</v>
+      </c>
+      <c r="B131" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A132">
+        <v>23005</v>
+      </c>
+      <c r="B132" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A133">
+        <v>23006</v>
+      </c>
+      <c r="B133" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A134">
+        <v>23007</v>
+      </c>
+      <c r="B134" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A135">
+        <v>23008</v>
+      </c>
+      <c r="B135" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A136">
+        <v>23009</v>
+      </c>
+      <c r="B136" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A137">
+        <v>23010</v>
+      </c>
+      <c r="B137" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A138">
+        <v>23011</v>
+      </c>
+      <c r="B138" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A139">
+        <v>24000</v>
+      </c>
+      <c r="B139" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A140">
+        <v>30000</v>
+      </c>
+      <c r="B140" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A141">
+        <v>30001</v>
+      </c>
+      <c r="B141" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A142">
+        <v>30002</v>
+      </c>
+      <c r="B142" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A143">
+        <v>30003</v>
+      </c>
+      <c r="B143" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A144">
+        <v>30004</v>
+      </c>
+      <c r="B144" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A145">
+        <v>30005</v>
+      </c>
+      <c r="B145" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A146">
+        <v>30006</v>
+      </c>
+      <c r="B146" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A147">
+        <v>30007</v>
+      </c>
+      <c r="B147" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A148">
+        <v>30008</v>
+      </c>
+      <c r="B148" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A149">
+        <v>30009</v>
+      </c>
+      <c r="B149" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A150">
+        <v>30010</v>
+      </c>
+      <c r="B150" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A151">
+        <v>30011</v>
+      </c>
+      <c r="B151" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A152">
+        <v>30012</v>
+      </c>
+      <c r="B152" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A153">
+        <v>30013</v>
+      </c>
+      <c r="B153" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A154">
+        <v>30014</v>
+      </c>
+      <c r="B154" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A155">
+        <v>30015</v>
+      </c>
+      <c r="B155" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A156">
+        <v>30016</v>
+      </c>
+      <c r="B156" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A157">
+        <v>30017</v>
+      </c>
+      <c r="B157" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A158">
+        <v>30018</v>
+      </c>
+      <c r="B158" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A159">
+        <v>30019</v>
+      </c>
+      <c r="B159" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A160">
+        <v>30020</v>
+      </c>
+      <c r="B160" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A161">
+        <v>30021</v>
+      </c>
+      <c r="B161" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A162">
+        <v>30022</v>
+      </c>
+      <c r="B162" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Data/Excel/TextData.xlsx
+++ b/Assets/Resources/Data/Excel/TextData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\grunge\Assets\Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A7F657-E4D8-4A2E-BF67-601216CA4204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB7A702-D967-416F-BC71-B1FD3EAF603B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4275" yWindow="3390" windowWidth="21600" windowHeight="10740" xr2:uid="{D3CC564E-66F4-4F1F-9FD0-0A2B28A7B6F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{D3CC564E-66F4-4F1F-9FD0-0A2B28A7B6F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -664,13 +664,148 @@
   <si>
     <t>Smiley Hag</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wrench Down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Your Jaw!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Push</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wrench Swing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wrench Throw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pattern Check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Endure!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sacrifice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Axe Down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Finish It!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uppercut</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Down Down!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Go Away</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Come Here</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>You Are Doomed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I'm Watching</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Highkick</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stab Down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eye Slice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neck Slice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Highknee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Front Shadow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Back Shadow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A expensive looks bracelet</t>
+  </si>
+  <si>
+    <t>A ring with a big diamond</t>
+  </si>
+  <si>
+    <t>Brochure of XTECH old version</t>
+  </si>
+  <si>
+    <t>Brochure of XTECH new version</t>
+  </si>
+  <si>
+    <t>VR gear for entertainment</t>
+  </si>
+  <si>
+    <t>Brochure of Xperience</t>
+  </si>
+  <si>
+    <t>Used MMA gloves</t>
+  </si>
+  <si>
+    <t>Used handcuffs with scratches</t>
+  </si>
+  <si>
+    <t>Brochure of Nine Pilgrims</t>
+  </si>
+  <si>
+    <t>A cross made by wood</t>
+  </si>
+  <si>
+    <t>Ring of Nine Pilgrims</t>
+  </si>
+  <si>
+    <t>Bible of Nine Pilgrims</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -683,6 +818,31 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -704,20 +864,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0] 2" xfId="1" xr:uid="{1486DB45-B437-47D0-BAD6-178CEE179632}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1030,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C61FB5-AAE8-41CA-A521-D7E0986A0FE0}">
-  <dimension ref="A1:B162"/>
+  <dimension ref="A1:B198"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="23.58203125" customWidth="1"/>
@@ -2132,204 +2305,492 @@
         <v>127</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A138">
+    <row r="138" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A138" s="4">
         <v>23011</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A139">
-        <v>24000</v>
+    <row r="139" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A139" s="3">
+        <v>23020</v>
       </c>
       <c r="B139" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A140">
-        <v>30000</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A140" s="3">
+        <v>23021</v>
       </c>
       <c r="B140" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A141">
-        <v>30001</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A141" s="3">
+        <v>23022</v>
       </c>
       <c r="B141" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A142">
-        <v>30002</v>
+        <v>189</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A142" s="3">
+        <v>23023</v>
       </c>
       <c r="B142" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A143">
-        <v>30003</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A143" s="3">
+        <v>23024</v>
       </c>
       <c r="B143" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A144">
-        <v>30004</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A144" s="3">
+        <v>23025</v>
       </c>
       <c r="B144" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A145">
-        <v>30005</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A145" s="3">
+        <v>23026</v>
       </c>
       <c r="B145" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A146">
-        <v>30006</v>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A146" s="3">
+        <v>23027</v>
       </c>
       <c r="B146" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A147">
-        <v>30007</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A147" s="3">
+        <v>23028</v>
       </c>
       <c r="B147" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A148">
-        <v>30008</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A148" s="3">
+        <v>23029</v>
       </c>
       <c r="B148" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A149">
-        <v>30009</v>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A149" s="3">
+        <v>23030</v>
       </c>
       <c r="B149" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A150">
-        <v>30010</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A150" s="3">
+        <v>23031</v>
       </c>
       <c r="B150" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A151">
-        <v>30011</v>
+        <v>24000</v>
       </c>
       <c r="B151" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A152">
-        <v>30012</v>
+        <v>30000</v>
       </c>
       <c r="B152" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A153">
-        <v>30013</v>
+        <v>30001</v>
       </c>
       <c r="B153" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A154">
-        <v>30014</v>
+        <v>30002</v>
       </c>
       <c r="B154" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A155">
-        <v>30015</v>
+        <v>30003</v>
       </c>
       <c r="B155" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A156">
-        <v>30016</v>
+        <v>30004</v>
       </c>
       <c r="B156" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A157">
-        <v>30017</v>
+        <v>30005</v>
       </c>
       <c r="B157" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A158">
-        <v>30018</v>
+        <v>30006</v>
       </c>
       <c r="B158" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A159">
-        <v>30019</v>
+        <v>30007</v>
       </c>
       <c r="B159" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A160">
-        <v>30020</v>
+        <v>30008</v>
       </c>
       <c r="B160" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A161">
-        <v>30021</v>
+        <v>30009</v>
       </c>
       <c r="B161" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A162">
+        <v>30010</v>
+      </c>
+      <c r="B162" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A163">
+        <v>30011</v>
+      </c>
+      <c r="B163" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A164">
+        <v>30012</v>
+      </c>
+      <c r="B164" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A165">
+        <v>30013</v>
+      </c>
+      <c r="B165" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A166">
+        <v>30014</v>
+      </c>
+      <c r="B166" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A167">
+        <v>30015</v>
+      </c>
+      <c r="B167" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A168">
+        <v>30016</v>
+      </c>
+      <c r="B168" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A169">
+        <v>30017</v>
+      </c>
+      <c r="B169" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A170">
+        <v>30018</v>
+      </c>
+      <c r="B170" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A171">
+        <v>30019</v>
+      </c>
+      <c r="B171" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A172">
+        <v>30020</v>
+      </c>
+      <c r="B172" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A173">
+        <v>30021</v>
+      </c>
+      <c r="B173" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A174">
         <v>30022</v>
       </c>
-      <c r="B162" t="s">
+      <c r="B174" t="s">
         <v>152</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A175">
+        <v>50000</v>
+      </c>
+      <c r="B175" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A176">
+        <v>50001</v>
+      </c>
+      <c r="B176" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A177">
+        <v>50002</v>
+      </c>
+      <c r="B177" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A178">
+        <v>50003</v>
+      </c>
+      <c r="B178" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A179">
+        <v>50004</v>
+      </c>
+      <c r="B179" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A180">
+        <v>50005</v>
+      </c>
+      <c r="B180" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A181">
+        <v>50006</v>
+      </c>
+      <c r="B181" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A182">
+        <v>50007</v>
+      </c>
+      <c r="B182" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A183">
+        <v>51000</v>
+      </c>
+      <c r="B183" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A184">
+        <v>51001</v>
+      </c>
+      <c r="B184" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A185">
+        <v>51002</v>
+      </c>
+      <c r="B185" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A186">
+        <v>51003</v>
+      </c>
+      <c r="B186" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A187">
+        <v>51004</v>
+      </c>
+      <c r="B187" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A188">
+        <v>51005</v>
+      </c>
+      <c r="B188" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A189">
+        <v>51006</v>
+      </c>
+      <c r="B189" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A190">
+        <v>51007</v>
+      </c>
+      <c r="B190" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A191">
+        <v>52000</v>
+      </c>
+      <c r="B191" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A192">
+        <v>52001</v>
+      </c>
+      <c r="B192" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A193">
+        <v>52002</v>
+      </c>
+      <c r="B193" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A194">
+        <v>52003</v>
+      </c>
+      <c r="B194" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A195">
+        <v>52004</v>
+      </c>
+      <c r="B195" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A196">
+        <v>52005</v>
+      </c>
+      <c r="B196" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A197">
+        <v>52006</v>
+      </c>
+      <c r="B197" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A198">
+        <v>52007</v>
+      </c>
+      <c r="B198" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
